--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/63.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/63.xlsx
@@ -426,13 +426,13 @@
         <v>-4.449361475606359</v>
       </c>
       <c r="E2">
-        <v>-24.76762119465115</v>
+        <v>-29.74758406088624</v>
       </c>
       <c r="F2">
-        <v>-6.499285831281844</v>
+        <v>-6.799944084871967</v>
       </c>
       <c r="G2">
-        <v>-15.07525885721185</v>
+        <v>-18.64102097319653</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.09559699369199</v>
       </c>
       <c r="E3">
-        <v>-26.38891904429931</v>
+        <v>-30.46110627519381</v>
       </c>
       <c r="F3">
-        <v>-6.04580827130787</v>
+        <v>-7.049255821198191</v>
       </c>
       <c r="G3">
-        <v>-15.03355591505365</v>
+        <v>-17.51778266663167</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.824846020935443</v>
       </c>
       <c r="E4">
-        <v>-26.47775864738179</v>
+        <v>-28.54660558320802</v>
       </c>
       <c r="F4">
-        <v>-5.866730724919555</v>
+        <v>-6.946421044990961</v>
       </c>
       <c r="G4">
-        <v>-14.26592482340792</v>
+        <v>-18.62719613502454</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.653792102301017</v>
       </c>
       <c r="E5">
-        <v>-26.77613979974719</v>
+        <v>-30.21694680635925</v>
       </c>
       <c r="F5">
-        <v>-5.964891193117364</v>
+        <v>-6.650784722858697</v>
       </c>
       <c r="G5">
-        <v>-15.12922902586582</v>
+        <v>-18.23835435343667</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.560369101021548</v>
       </c>
       <c r="E6">
-        <v>-27.04356430379616</v>
+        <v>-31.39074538304344</v>
       </c>
       <c r="F6">
-        <v>-5.79528658366225</v>
+        <v>-6.98049487368812</v>
       </c>
       <c r="G6">
-        <v>-15.12023592890839</v>
+        <v>-18.36838761640093</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.529461326070669</v>
       </c>
       <c r="E7">
-        <v>-26.97088229597305</v>
+        <v>-31.44441232850834</v>
       </c>
       <c r="F7">
-        <v>-6.001799459476681</v>
+        <v>-6.227718671652428</v>
       </c>
       <c r="G7">
-        <v>-14.37300938469395</v>
+        <v>-17.82474472539675</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.537087288880641</v>
       </c>
       <c r="E8">
-        <v>-27.00454697174607</v>
+        <v>-32.46456431058628</v>
       </c>
       <c r="F8">
-        <v>-5.890380205354812</v>
+        <v>-6.694131941543711</v>
       </c>
       <c r="G8">
-        <v>-14.12594999218922</v>
+        <v>-17.61437445383099</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.560124083622808</v>
       </c>
       <c r="E9">
-        <v>-27.777322004207</v>
+        <v>-33.11648795720451</v>
       </c>
       <c r="F9">
-        <v>-5.617077699968553</v>
+        <v>-6.588045421165606</v>
       </c>
       <c r="G9">
-        <v>-14.68800944802837</v>
+        <v>-18.00680155623789</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.582202755384763</v>
       </c>
       <c r="E10">
-        <v>-27.80698350895724</v>
+        <v>-33.06309272018007</v>
       </c>
       <c r="F10">
-        <v>-5.689704869544691</v>
+        <v>-6.152560740023418</v>
       </c>
       <c r="G10">
-        <v>-14.33576078155884</v>
+        <v>-18.45390562877139</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.589782565740678</v>
       </c>
       <c r="E11">
-        <v>-28.95104359683306</v>
+        <v>-32.99896047128345</v>
       </c>
       <c r="F11">
-        <v>-5.13198541065762</v>
+        <v>-6.180064960656855</v>
       </c>
       <c r="G11">
-        <v>-14.40974816381601</v>
+        <v>-18.17140519099599</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.5736354859073</v>
       </c>
       <c r="E12">
-        <v>-29.54507070326322</v>
+        <v>-32.60642328735056</v>
       </c>
       <c r="F12">
-        <v>-5.80654831642694</v>
+        <v>-5.869381056769043</v>
       </c>
       <c r="G12">
-        <v>-14.64637768259927</v>
+        <v>-18.34291131320347</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.528196646362655</v>
       </c>
       <c r="E13">
-        <v>-29.28513176674894</v>
+        <v>-34.24115485514248</v>
       </c>
       <c r="F13">
-        <v>-5.785158784333015</v>
+        <v>-6.259538094978959</v>
       </c>
       <c r="G13">
-        <v>-14.0651683760882</v>
+        <v>-17.99408740609432</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.461618324088424</v>
       </c>
       <c r="E14">
-        <v>-29.69043245467244</v>
+        <v>-34.39620754092811</v>
       </c>
       <c r="F14">
-        <v>-5.576633810153019</v>
+        <v>-6.772308416647548</v>
       </c>
       <c r="G14">
-        <v>-13.16512704978101</v>
+        <v>-17.71481971603801</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.38409434028783</v>
       </c>
       <c r="E15">
-        <v>-30.5991341629476</v>
+        <v>-34.89492385491884</v>
       </c>
       <c r="F15">
-        <v>-5.258665254980664</v>
+        <v>-6.093629459204001</v>
       </c>
       <c r="G15">
-        <v>-13.55639711652193</v>
+        <v>-16.7336849214736</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.308708363858603</v>
       </c>
       <c r="E16">
-        <v>-30.53870847002625</v>
+        <v>-35.44406925545898</v>
       </c>
       <c r="F16">
-        <v>-5.321557384294595</v>
+        <v>-5.549821669004628</v>
       </c>
       <c r="G16">
-        <v>-12.69348355843766</v>
+        <v>-17.49593968716356</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.245961841592899</v>
       </c>
       <c r="E17">
-        <v>-31.65745438819919</v>
+        <v>-34.83361963804</v>
       </c>
       <c r="F17">
-        <v>-4.917861244213587</v>
+        <v>-5.443885996614968</v>
       </c>
       <c r="G17">
-        <v>-13.31678645148056</v>
+        <v>-16.05095277018247</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.212359104748771</v>
       </c>
       <c r="E18">
-        <v>-30.9288636766311</v>
+        <v>-35.76459464572189</v>
       </c>
       <c r="F18">
-        <v>-5.27099757294419</v>
+        <v>-5.843203189839786</v>
       </c>
       <c r="G18">
-        <v>-12.00182121055435</v>
+        <v>-16.15852398166278</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.219767695639854</v>
       </c>
       <c r="E19">
-        <v>-32.61765843136359</v>
+        <v>-35.92428901736538</v>
       </c>
       <c r="F19">
-        <v>-4.493227720077512</v>
+        <v>-5.522634981407237</v>
       </c>
       <c r="G19">
-        <v>-11.91427383376832</v>
+        <v>-16.3988679325411</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.275485013107326</v>
       </c>
       <c r="E20">
-        <v>-33.42160747889333</v>
+        <v>-36.46064374307086</v>
       </c>
       <c r="F20">
-        <v>-4.637538962357143</v>
+        <v>-4.775151128614465</v>
       </c>
       <c r="G20">
-        <v>-11.67485849091377</v>
+        <v>-15.55196251741198</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.377994891443791</v>
       </c>
       <c r="E21">
-        <v>-33.36708918031498</v>
+        <v>-35.48085404982329</v>
       </c>
       <c r="F21">
-        <v>-4.462510160141648</v>
+        <v>-4.864327233153987</v>
       </c>
       <c r="G21">
-        <v>-13.01551356522472</v>
+        <v>-15.8710676572151</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.528536463364348</v>
       </c>
       <c r="E22">
-        <v>-33.28872393761225</v>
+        <v>-36.22204976879173</v>
       </c>
       <c r="F22">
-        <v>-4.468878241627631</v>
+        <v>-4.98899656281738</v>
       </c>
       <c r="G22">
-        <v>-11.52698635331114</v>
+        <v>-15.18601315822817</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.723102314901333</v>
       </c>
       <c r="E23">
-        <v>-35.05590657741751</v>
+        <v>-38.30884531134736</v>
       </c>
       <c r="F23">
-        <v>-3.989651999027485</v>
+        <v>-5.03636995786592</v>
       </c>
       <c r="G23">
-        <v>-11.80812450159713</v>
+        <v>-15.27855283768742</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.953199499140325</v>
       </c>
       <c r="E24">
-        <v>-35.6957618408053</v>
+        <v>-40.60285476754596</v>
       </c>
       <c r="F24">
-        <v>-3.837530711025864</v>
+        <v>-4.971471273157127</v>
       </c>
       <c r="G24">
-        <v>-11.48931234507423</v>
+        <v>-14.91510790620407</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.20380416653826</v>
       </c>
       <c r="E25">
-        <v>-35.88057339353234</v>
+        <v>-38.47192924578559</v>
       </c>
       <c r="F25">
-        <v>-3.623044667780153</v>
+        <v>-5.383136621404627</v>
       </c>
       <c r="G25">
-        <v>-11.62196590483283</v>
+        <v>-15.46181636237762</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.46516149515136</v>
       </c>
       <c r="E26">
-        <v>-35.24974337884183</v>
+        <v>-38.59058658597157</v>
       </c>
       <c r="F26">
-        <v>-3.728064166297731</v>
+        <v>-4.818288110339205</v>
       </c>
       <c r="G26">
-        <v>-11.7790976383088</v>
+        <v>-15.28706425026888</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.726303856885613</v>
       </c>
       <c r="E27">
-        <v>-34.7215082070321</v>
+        <v>-38.29737015821192</v>
       </c>
       <c r="F27">
-        <v>-4.012559513241358</v>
+        <v>-4.689016531285545</v>
       </c>
       <c r="G27">
-        <v>-12.05332005696325</v>
+        <v>-14.97795364744882</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.975015423023063</v>
       </c>
       <c r="E28">
-        <v>-34.20701242536165</v>
+        <v>-40.23426188992864</v>
       </c>
       <c r="F28">
-        <v>-3.803012256892946</v>
+        <v>-5.052628282793822</v>
       </c>
       <c r="G28">
-        <v>-11.59145922768845</v>
+        <v>-13.99972220132235</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.196360325951155</v>
       </c>
       <c r="E29">
-        <v>-34.86407136150458</v>
+        <v>-39.25357555882755</v>
       </c>
       <c r="F29">
-        <v>-4.164612701888616</v>
+        <v>-4.085654667915509</v>
       </c>
       <c r="G29">
-        <v>-11.88875945929716</v>
+        <v>-14.989348545195</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.38234508717991</v>
       </c>
       <c r="E30">
-        <v>-35.79877556753178</v>
+        <v>-38.15846827497465</v>
       </c>
       <c r="F30">
-        <v>-3.795070763579975</v>
+        <v>-4.645310999137162</v>
       </c>
       <c r="G30">
-        <v>-11.88073469690996</v>
+        <v>-15.66977986733633</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.526321069897853</v>
       </c>
       <c r="E31">
-        <v>-34.71049722248245</v>
+        <v>-39.01495667794138</v>
       </c>
       <c r="F31">
-        <v>-3.893569352990731</v>
+        <v>-4.64624934489206</v>
       </c>
       <c r="G31">
-        <v>-12.01761582332221</v>
+        <v>-15.41580971101837</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.621754130245919</v>
       </c>
       <c r="E32">
-        <v>-34.99451179105852</v>
+        <v>-38.54089790492241</v>
       </c>
       <c r="F32">
-        <v>-3.881360564088608</v>
+        <v>-4.633677095482344</v>
       </c>
       <c r="G32">
-        <v>-12.14346290145206</v>
+        <v>-14.78323397991997</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.660769940057379</v>
       </c>
       <c r="E33">
-        <v>-34.23198243103995</v>
+        <v>-39.17942632542596</v>
       </c>
       <c r="F33">
-        <v>-4.179659491791205</v>
+        <v>-5.008548996049396</v>
       </c>
       <c r="G33">
-        <v>-11.94545917274825</v>
+        <v>-15.49132822058746</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.642204860258913</v>
       </c>
       <c r="E34">
-        <v>-35.00603222893403</v>
+        <v>-37.75943725931477</v>
       </c>
       <c r="F34">
-        <v>-3.685975597889013</v>
+        <v>-4.767076604004597</v>
       </c>
       <c r="G34">
-        <v>-11.88691879597732</v>
+        <v>-15.53471623042514</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.566463089138941</v>
       </c>
       <c r="E35">
-        <v>-33.85451148013058</v>
+        <v>-37.00459045545021</v>
       </c>
       <c r="F35">
-        <v>-4.104292510981358</v>
+        <v>-4.55760378183421</v>
       </c>
       <c r="G35">
-        <v>-12.54470764190281</v>
+        <v>-15.80486502279352</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.434307801346857</v>
       </c>
       <c r="E36">
-        <v>-33.1486016306299</v>
+        <v>-38.46852383333182</v>
       </c>
       <c r="F36">
-        <v>-3.651472188962291</v>
+        <v>-4.605696971221318</v>
       </c>
       <c r="G36">
-        <v>-12.29020945357134</v>
+        <v>-14.46162772296193</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.245862871495565</v>
       </c>
       <c r="E37">
-        <v>-33.55393628210847</v>
+        <v>-38.61686305640108</v>
       </c>
       <c r="F37">
-        <v>-3.918451748481158</v>
+        <v>-4.65544117402527</v>
       </c>
       <c r="G37">
-        <v>-11.864847388867</v>
+        <v>-15.21288982218874</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.008064888273632</v>
       </c>
       <c r="E38">
-        <v>-33.36756919855979</v>
+        <v>-37.86060789712013</v>
       </c>
       <c r="F38">
-        <v>-4.019877818276604</v>
+        <v>-4.740900320781257</v>
       </c>
       <c r="G38">
-        <v>-11.86569819907059</v>
+        <v>-15.21470234587149</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.728071165379148</v>
       </c>
       <c r="E39">
-        <v>-33.46037121639898</v>
+        <v>-36.79405037764859</v>
       </c>
       <c r="F39">
-        <v>-3.877330824386773</v>
+        <v>-4.948709459887474</v>
       </c>
       <c r="G39">
-        <v>-11.72042152917076</v>
+        <v>-15.00250134262252</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.412413179186845</v>
       </c>
       <c r="E40">
-        <v>-32.86990122630184</v>
+        <v>-36.90166729820388</v>
       </c>
       <c r="F40">
-        <v>-3.745447714278553</v>
+        <v>-4.558280816113061</v>
       </c>
       <c r="G40">
-        <v>-12.14127794139615</v>
+        <v>-14.45755906249417</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.06606141780047</v>
       </c>
       <c r="E41">
-        <v>-32.47327709457704</v>
+        <v>-36.75055438480491</v>
       </c>
       <c r="F41">
-        <v>-3.876675961990738</v>
+        <v>-4.154402549851778</v>
       </c>
       <c r="G41">
-        <v>-12.32166956783103</v>
+        <v>-15.5947000050512</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.699536143722055</v>
       </c>
       <c r="E42">
-        <v>-31.5815367856976</v>
+        <v>-36.04758804340923</v>
       </c>
       <c r="F42">
-        <v>-3.637131731897987</v>
+        <v>-4.525774460345708</v>
       </c>
       <c r="G42">
-        <v>-11.917365883302</v>
+        <v>-15.65245412725655</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.321814936514599</v>
       </c>
       <c r="E43">
-        <v>-31.28657236697099</v>
+        <v>-36.0608564722517</v>
       </c>
       <c r="F43">
-        <v>-3.403089296155473</v>
+        <v>-4.347203699850334</v>
       </c>
       <c r="G43">
-        <v>-11.79205511354951</v>
+        <v>-14.92113309908554</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.94004527128403</v>
       </c>
       <c r="E44">
-        <v>-31.28228616632273</v>
+        <v>-35.21526584198443</v>
       </c>
       <c r="F44">
-        <v>-3.562853548905004</v>
+        <v>-4.484566432425973</v>
       </c>
       <c r="G44">
-        <v>-12.41962198924699</v>
+        <v>-15.32436747740539</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.558843044705152</v>
       </c>
       <c r="E45">
-        <v>-30.6510304750755</v>
+        <v>-34.27437347622575</v>
       </c>
       <c r="F45">
-        <v>-3.863052923706128</v>
+        <v>-4.591449952806024</v>
       </c>
       <c r="G45">
-        <v>-12.0745174800512</v>
+        <v>-16.49064949707186</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.186593492104784</v>
       </c>
       <c r="E46">
-        <v>-30.21891216407858</v>
+        <v>-35.3467251781901</v>
       </c>
       <c r="F46">
-        <v>-3.310996005319711</v>
+        <v>-4.367844930899214</v>
       </c>
       <c r="G46">
-        <v>-11.50016431335197</v>
+        <v>-15.0842999570796</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.828277242400581</v>
       </c>
       <c r="E47">
-        <v>-29.4625234148144</v>
+        <v>-35.44627915077473</v>
       </c>
       <c r="F47">
-        <v>-3.59590390765431</v>
+        <v>-4.265627799999005</v>
       </c>
       <c r="G47">
-        <v>-12.70186254919755</v>
+        <v>-16.29170391816212</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.486491368251193</v>
       </c>
       <c r="E48">
-        <v>-30.25489541854353</v>
+        <v>-35.60509952693474</v>
       </c>
       <c r="F48">
-        <v>-3.390526548981249</v>
+        <v>-4.20147979189413</v>
       </c>
       <c r="G48">
-        <v>-12.00380422733237</v>
+        <v>-14.99249190818453</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.161942989036869</v>
       </c>
       <c r="E49">
-        <v>-28.76499124222792</v>
+        <v>-33.32001116453124</v>
       </c>
       <c r="F49">
-        <v>-3.379826239963582</v>
+        <v>-4.560089408268492</v>
       </c>
       <c r="G49">
-        <v>-12.69104368637521</v>
+        <v>-14.98779920988262</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.8587790920239214</v>
       </c>
       <c r="E50">
-        <v>-28.63083972822469</v>
+        <v>-33.79496883964072</v>
       </c>
       <c r="F50">
-        <v>-3.509939558711299</v>
+        <v>-4.084554784157236</v>
       </c>
       <c r="G50">
-        <v>-12.67862583005741</v>
+        <v>-15.70902638470439</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.5782273199357094</v>
       </c>
       <c r="E51">
-        <v>-28.44787126441878</v>
+        <v>-32.83360550713036</v>
       </c>
       <c r="F51">
-        <v>-3.35515764477174</v>
+        <v>-3.863207335032884</v>
       </c>
       <c r="G51">
-        <v>-12.1866522785574</v>
+        <v>-15.16083314885647</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.3194008807132579</v>
       </c>
       <c r="E52">
-        <v>-28.41096420125627</v>
+        <v>-33.57882477525462</v>
       </c>
       <c r="F52">
-        <v>-3.709987746978906</v>
+        <v>-4.626665237541736</v>
       </c>
       <c r="G52">
-        <v>-13.25939483401175</v>
+        <v>-15.72473161274269</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.08029485815361685</v>
       </c>
       <c r="E53">
-        <v>-28.7983389248204</v>
+        <v>-32.6424020133415</v>
       </c>
       <c r="F53">
-        <v>-3.662967518349509</v>
+        <v>-4.693478622702295</v>
       </c>
       <c r="G53">
-        <v>-12.74081111746708</v>
+        <v>-16.13860111860745</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.1385629651433859</v>
       </c>
       <c r="E54">
-        <v>-28.59616973122197</v>
+        <v>-31.45181411927388</v>
       </c>
       <c r="F54">
-        <v>-3.536879188185881</v>
+        <v>-3.926767788243131</v>
       </c>
       <c r="G54">
-        <v>-12.85968287614569</v>
+        <v>-15.46870560764485</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.338461440285428</v>
       </c>
       <c r="E55">
-        <v>-28.29214610024301</v>
+        <v>-32.70155067659269</v>
       </c>
       <c r="F55">
-        <v>-3.727819483733796</v>
+        <v>-4.432871103934199</v>
       </c>
       <c r="G55">
-        <v>-12.1736285924059</v>
+        <v>-15.33239223979258</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.5217090391191571</v>
       </c>
       <c r="E56">
-        <v>-26.36526229608324</v>
+        <v>-31.35883775518539</v>
       </c>
       <c r="F56">
-        <v>-3.62031990175264</v>
+        <v>-4.386731415793786</v>
       </c>
       <c r="G56">
-        <v>-12.91789550890823</v>
+        <v>-14.81739384406694</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.6904950079248136</v>
       </c>
       <c r="E57">
-        <v>-27.38209943518757</v>
+        <v>-32.92649130173869</v>
       </c>
       <c r="F57">
-        <v>-3.617809727876668</v>
+        <v>-4.293245255605396</v>
       </c>
       <c r="G57">
-        <v>-12.78428189094325</v>
+        <v>-16.93504223280869</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.8451404856690268</v>
       </c>
       <c r="E58">
-        <v>-25.9847934953808</v>
+        <v>-31.51464896036731</v>
       </c>
       <c r="F58">
-        <v>-3.372158727773982</v>
+        <v>-4.29488280752196</v>
       </c>
       <c r="G58">
-        <v>-13.40078492344849</v>
+        <v>-15.05300537009687</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.9880870960790084</v>
       </c>
       <c r="E59">
-        <v>-26.55086180328761</v>
+        <v>-30.85194301713681</v>
       </c>
       <c r="F59">
-        <v>-3.716717705266566</v>
+        <v>-4.372251592608923</v>
       </c>
       <c r="G59">
-        <v>-13.40915067202623</v>
+        <v>-16.82191923645903</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.122071530533069</v>
       </c>
       <c r="E60">
-        <v>-26.62877872706359</v>
+        <v>-29.4690738524665</v>
       </c>
       <c r="F60">
-        <v>-3.645664739370375</v>
+        <v>-5.008590172403197</v>
       </c>
       <c r="G60">
-        <v>-12.83202326816508</v>
+        <v>-16.62738992529868</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.249466488799497</v>
       </c>
       <c r="E61">
-        <v>-26.17213193660412</v>
+        <v>-30.91262004036559</v>
       </c>
       <c r="F61">
-        <v>-3.861899985799688</v>
+        <v>-4.718483755401168</v>
       </c>
       <c r="G61">
-        <v>-13.27358052164753</v>
+        <v>-15.93921027132268</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.371344073957872</v>
       </c>
       <c r="E62">
-        <v>-25.75741428698167</v>
+        <v>-29.85689010224639</v>
       </c>
       <c r="F62">
-        <v>-3.512204258170377</v>
+        <v>-4.65999749594399</v>
       </c>
       <c r="G62">
-        <v>-12.45377357703011</v>
+        <v>-16.11425867725719</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.490602513187856</v>
       </c>
       <c r="E63">
-        <v>-25.81826792069674</v>
+        <v>-28.19526845579692</v>
       </c>
       <c r="F63">
-        <v>-3.820676912673757</v>
+        <v>-5.300103712111095</v>
       </c>
       <c r="G63">
-        <v>-13.26582722399456</v>
+        <v>-16.73637473972426</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>1.609140117283664</v>
       </c>
       <c r="E64">
-        <v>-25.62797691442043</v>
+        <v>-29.50818854670775</v>
       </c>
       <c r="F64">
-        <v>-4.112105724115178</v>
+        <v>-4.829202219655456</v>
       </c>
       <c r="G64">
-        <v>-13.3140420092285</v>
+        <v>-16.56944379145205</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>1.727313891560359</v>
       </c>
       <c r="E65">
-        <v>-25.40194719127557</v>
+        <v>-30.38774046779554</v>
       </c>
       <c r="F65">
-        <v>-3.822267745265816</v>
+        <v>-4.969016528988196</v>
       </c>
       <c r="G65">
-        <v>-13.20668101738994</v>
+        <v>-16.92696615696564</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>1.84375994053192</v>
       </c>
       <c r="E66">
-        <v>-25.17733488049512</v>
+        <v>-31.14923959997737</v>
       </c>
       <c r="F66">
-        <v>-3.747588092823269</v>
+        <v>-4.971346952242766</v>
       </c>
       <c r="G66">
-        <v>-13.5330610810156</v>
+        <v>-16.82791794497619</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>1.958758779142425</v>
       </c>
       <c r="E67">
-        <v>-25.64595042775687</v>
+        <v>-30.41967300226063</v>
       </c>
       <c r="F67">
-        <v>-4.001277192299768</v>
+        <v>-5.088672637576266</v>
       </c>
       <c r="G67">
-        <v>-13.341860523395</v>
+        <v>-16.24755282757763</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>2.07096585561722</v>
       </c>
       <c r="E68">
-        <v>-25.61612589794235</v>
+        <v>-29.97447645832955</v>
       </c>
       <c r="F68">
-        <v>-4.049520041895884</v>
+        <v>-5.109095317208816</v>
       </c>
       <c r="G68">
-        <v>-12.75289129813988</v>
+        <v>-16.32297202078054</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>2.178017789273492</v>
       </c>
       <c r="E69">
-        <v>-25.25211357178378</v>
+        <v>-29.71760782719247</v>
       </c>
       <c r="F69">
-        <v>-4.088715179597095</v>
+        <v>-5.147194530416543</v>
       </c>
       <c r="G69">
-        <v>-13.1433436601326</v>
+        <v>-17.28723627527683</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>2.276621299245793</v>
       </c>
       <c r="E70">
-        <v>-25.82731581176407</v>
+        <v>-29.58113547026031</v>
       </c>
       <c r="F70">
-        <v>-4.019130309084517</v>
+        <v>-5.163779890615982</v>
       </c>
       <c r="G70">
-        <v>-12.84003809891565</v>
+        <v>-16.81202401584214</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>2.365974265113512</v>
       </c>
       <c r="E71">
-        <v>-25.80563800668935</v>
+        <v>-28.74708112752758</v>
       </c>
       <c r="F71">
-        <v>-4.127360771345649</v>
+        <v>-5.750402774312781</v>
       </c>
       <c r="G71">
-        <v>-13.59935144489397</v>
+        <v>-16.01572525509909</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>2.443661472314727</v>
       </c>
       <c r="E72">
-        <v>-25.95954725278804</v>
+        <v>-29.15077194294136</v>
       </c>
       <c r="F72">
-        <v>-4.252260530219738</v>
+        <v>-4.962249353611524</v>
       </c>
       <c r="G72">
-        <v>-13.38526508596038</v>
+        <v>-16.96765110637051</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>2.506935070347527</v>
       </c>
       <c r="E73">
-        <v>-25.8621669477271</v>
+        <v>-28.63112049361317</v>
       </c>
       <c r="F73">
-        <v>-4.487745722051218</v>
+        <v>-5.298817742907757</v>
       </c>
       <c r="G73">
-        <v>-13.49635044153063</v>
+        <v>-16.12127703380044</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>2.553394312303725</v>
       </c>
       <c r="E74">
-        <v>-25.75829281093916</v>
+        <v>-28.24853236707514</v>
       </c>
       <c r="F74">
-        <v>-4.596776747652605</v>
+        <v>-5.438135560436008</v>
       </c>
       <c r="G74">
-        <v>-13.05314122582408</v>
+        <v>-14.65392572642881</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>2.584202609294385</v>
       </c>
       <c r="E75">
-        <v>-25.41805950179486</v>
+        <v>-29.2816855980291</v>
       </c>
       <c r="F75">
-        <v>-4.279557285378253</v>
+        <v>-5.458433127301237</v>
       </c>
       <c r="G75">
-        <v>-12.86145070746366</v>
+        <v>-16.4477448268829</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>2.599281297480479</v>
       </c>
       <c r="E76">
-        <v>-27.76159008550435</v>
+        <v>-30.73346002320012</v>
       </c>
       <c r="F76">
-        <v>-4.396274035787266</v>
+        <v>-5.346014554746726</v>
       </c>
       <c r="G76">
-        <v>-12.65604790947958</v>
+        <v>-17.17844843831084</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>2.597630974517256</v>
       </c>
       <c r="E77">
-        <v>-25.99903101766092</v>
+        <v>-30.46705442580289</v>
       </c>
       <c r="F77">
-        <v>-4.785731867835517</v>
+        <v>-5.41807713316401</v>
       </c>
       <c r="G77">
-        <v>-12.31939853359109</v>
+        <v>-16.63959756197475</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>2.578048650476153</v>
       </c>
       <c r="E78">
-        <v>-26.18843897150574</v>
+        <v>-30.13661167746318</v>
       </c>
       <c r="F78">
-        <v>-4.735248866222011</v>
+        <v>-5.455345692619089</v>
       </c>
       <c r="G78">
-        <v>-12.15607276941115</v>
+        <v>-15.44353056409146</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>2.541198537045674</v>
       </c>
       <c r="E79">
-        <v>-26.80121396032766</v>
+        <v>-30.77148788367954</v>
       </c>
       <c r="F79">
-        <v>-4.85056799616065</v>
+        <v>-5.217750212655285</v>
       </c>
       <c r="G79">
-        <v>-13.2673732487614</v>
+        <v>-15.37718723148446</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.48551324850835</v>
       </c>
       <c r="E80">
-        <v>-27.56144059131334</v>
+        <v>-31.40387569342868</v>
       </c>
       <c r="F80">
-        <v>-4.966896738620381</v>
+        <v>-5.56246518518054</v>
       </c>
       <c r="G80">
-        <v>-12.35939654479657</v>
+        <v>-14.64461150655407</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.408094509872146</v>
       </c>
       <c r="E81">
-        <v>-27.5056860193309</v>
+        <v>-31.85893298951146</v>
       </c>
       <c r="F81">
-        <v>-4.748553579617617</v>
+        <v>-5.847229762129791</v>
       </c>
       <c r="G81">
-        <v>-12.63896549449694</v>
+        <v>-16.2524557455213</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.306252676706383</v>
       </c>
       <c r="E82">
-        <v>-27.20071140881033</v>
+        <v>-31.91767861857596</v>
       </c>
       <c r="F82">
-        <v>-4.929199786715175</v>
+        <v>-5.873480479531158</v>
       </c>
       <c r="G82">
-        <v>-12.58149111338965</v>
+        <v>-15.579425147933</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.177394374504448</v>
       </c>
       <c r="E83">
-        <v>-28.9106858364767</v>
+        <v>-32.9903722203279</v>
       </c>
       <c r="F83">
-        <v>-4.989702103802709</v>
+        <v>-5.547272694333729</v>
       </c>
       <c r="G83">
-        <v>-11.73406097679255</v>
+        <v>-15.08108045154266</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.016723830210664</v>
       </c>
       <c r="E84">
-        <v>-30.29764421317594</v>
+        <v>-34.47644983610702</v>
       </c>
       <c r="F84">
-        <v>-4.94324488262625</v>
+        <v>-5.639099130722739</v>
       </c>
       <c r="G84">
-        <v>-12.31337334070962</v>
+        <v>-15.39981149969984</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.818403517217207</v>
       </c>
       <c r="E85">
-        <v>-30.58750504169591</v>
+        <v>-35.05071015349371</v>
       </c>
       <c r="F85">
-        <v>-4.771119805206714</v>
+        <v>-5.47178456002135</v>
       </c>
       <c r="G85">
-        <v>-12.70133948300235</v>
+        <v>-15.4333671892859</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.57907903357776</v>
       </c>
       <c r="E86">
-        <v>-31.15949885784175</v>
+        <v>-35.44902567026038</v>
       </c>
       <c r="F86">
-        <v>-5.033813064665444</v>
+        <v>-5.266650300206309</v>
       </c>
       <c r="G86">
-        <v>-12.15631774978105</v>
+        <v>-14.74256889378833</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.293715215396912</v>
       </c>
       <c r="E87">
-        <v>-32.76066764052582</v>
+        <v>-35.47842678775518</v>
       </c>
       <c r="F87">
-        <v>-5.149861491178142</v>
+        <v>-5.458920116870235</v>
       </c>
       <c r="G87">
-        <v>-11.63260268765051</v>
+        <v>-15.50785611919227</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.9567475477171488</v>
       </c>
       <c r="E88">
-        <v>-32.73322961651335</v>
+        <v>-36.82327035618308</v>
       </c>
       <c r="F88">
-        <v>-4.835765096969037</v>
+        <v>-5.954659661050668</v>
       </c>
       <c r="G88">
-        <v>-12.10337881606257</v>
+        <v>-15.50079969137531</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.5631448881659752</v>
       </c>
       <c r="E89">
-        <v>-34.24328097368908</v>
+        <v>-35.91711817877424</v>
       </c>
       <c r="F89">
-        <v>-4.759663276614425</v>
+        <v>-5.412327488838007</v>
       </c>
       <c r="G89">
-        <v>-11.88733923526081</v>
+        <v>-14.79446169511641</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.1143198508825245</v>
       </c>
       <c r="E90">
-        <v>-35.80895557710103</v>
+        <v>-38.31719808165451</v>
       </c>
       <c r="F90">
-        <v>-5.086187011141984</v>
+        <v>-6.022842159975125</v>
       </c>
       <c r="G90">
-        <v>-11.4683698339928</v>
+        <v>-15.33325960272387</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.3918381690551331</v>
       </c>
       <c r="E91">
-        <v>-36.75969737382641</v>
+        <v>-40.27009117627733</v>
       </c>
       <c r="F91">
-        <v>-5.092376925712479</v>
+        <v>-6.144055447404551</v>
       </c>
       <c r="G91">
-        <v>-11.58071650741351</v>
+        <v>-14.69809005919546</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.955277610683232</v>
       </c>
       <c r="E92">
-        <v>-37.99721157979851</v>
+        <v>-40.40915608457888</v>
       </c>
       <c r="F92">
-        <v>-4.83110029119511</v>
+        <v>-5.230955944431178</v>
       </c>
       <c r="G92">
-        <v>-11.66533736194282</v>
+        <v>-15.14729301760085</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.573976825149592</v>
       </c>
       <c r="E93">
-        <v>-38.8578729715633</v>
+        <v>-42.80515130390423</v>
       </c>
       <c r="F93">
-        <v>-5.120551845801105</v>
+        <v>-5.479393475092079</v>
       </c>
       <c r="G93">
-        <v>-12.08809733785329</v>
+        <v>-14.86338228742573</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.237169171051031</v>
       </c>
       <c r="E94">
-        <v>-40.01128209402795</v>
+        <v>-44.43645708110935</v>
       </c>
       <c r="F94">
-        <v>-5.466703239591663</v>
+        <v>-5.415994559885207</v>
       </c>
       <c r="G94">
-        <v>-12.42552469194351</v>
+        <v>-16.21967141304589</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.939111621027946</v>
       </c>
       <c r="E95">
-        <v>-41.35611207703383</v>
+        <v>-43.89690298851745</v>
       </c>
       <c r="F95">
-        <v>-5.110313187057788</v>
+        <v>-5.870162615638312</v>
       </c>
       <c r="G95">
-        <v>-12.70614639512537</v>
+        <v>-15.65789004303204</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.676153067299425</v>
       </c>
       <c r="E96">
-        <v>-43.86610936526529</v>
+        <v>-46.8069501990605</v>
       </c>
       <c r="F96">
-        <v>-5.212643552930951</v>
+        <v>-5.743042501070776</v>
       </c>
       <c r="G96">
-        <v>-12.85422378655143</v>
+        <v>-15.22279994026055</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.433410498114855</v>
       </c>
       <c r="E97">
-        <v>-45.65977225683041</v>
+        <v>-48.72856512371234</v>
       </c>
       <c r="F97">
-        <v>-5.103001216846205</v>
+        <v>-5.711372342026776</v>
       </c>
       <c r="G97">
-        <v>-13.03779684724956</v>
+        <v>-15.60952297270329</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.205152945448359</v>
       </c>
       <c r="E98">
-        <v>-47.53789345287558</v>
+        <v>-49.83064172906305</v>
       </c>
       <c r="F98">
-        <v>-5.437177418357167</v>
+        <v>-5.823204151539617</v>
       </c>
       <c r="G98">
-        <v>-12.67396127139258</v>
+        <v>-15.68384637533269</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.965145563343996</v>
       </c>
       <c r="E99">
-        <v>-48.95996561703029</v>
+        <v>-51.12485242961119</v>
       </c>
       <c r="F99">
-        <v>-5.532759613324642</v>
+        <v>-5.639989173447216</v>
       </c>
       <c r="G99">
-        <v>-12.74077139092061</v>
+        <v>-16.52453955175737</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.729017397251341</v>
       </c>
       <c r="E100">
-        <v>-50.37735986753508</v>
+        <v>-52.05311261712549</v>
       </c>
       <c r="F100">
-        <v>-5.50300336287945</v>
+        <v>-5.228257309551268</v>
       </c>
       <c r="G100">
-        <v>-12.99648454946499</v>
+        <v>-15.36883141454334</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.4417276156955</v>
       </c>
       <c r="E101">
-        <v>-52.32767059985503</v>
+        <v>-54.01074249556033</v>
       </c>
       <c r="F101">
-        <v>-5.38830267010079</v>
+        <v>-5.354272789242785</v>
       </c>
       <c r="G101">
-        <v>-13.58551667508536</v>
+        <v>-16.74438294938376</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.156527301533069</v>
       </c>
       <c r="E102">
-        <v>-54.62828709963083</v>
+        <v>-56.07094910297992</v>
       </c>
       <c r="F102">
-        <v>-5.472085464145284</v>
+        <v>-5.696932111489799</v>
       </c>
       <c r="G102">
-        <v>-13.86785324085656</v>
+        <v>-16.22077382471047</v>
       </c>
     </row>
   </sheetData>
